--- a/PAMF_DIG F2 - monthly2026-07-18.xlsx
+++ b/PAMF_DIG F2 - monthly2026-07-18.xlsx
@@ -1801,7 +1801,7 @@
         <v>0.09</v>
       </c>
       <c r="N19" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -5451,7 +5451,7 @@
         <v>0.09</v>
       </c>
       <c r="N69" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
@@ -6254,7 +6254,7 @@
         <v>0.09</v>
       </c>
       <c r="N80" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
@@ -8006,7 +8006,7 @@
         <v>0.09</v>
       </c>
       <c r="N104" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
@@ -9247,7 +9247,7 @@
         <v>0.09</v>
       </c>
       <c r="N121" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O121" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
         <v>0.09</v>
       </c>
       <c r="N156" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O156" t="inlineStr">
         <is>
@@ -13627,7 +13627,7 @@
         <v>0.09</v>
       </c>
       <c r="N181" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O181" t="inlineStr">
         <is>

--- a/PAMF_DIG F2 - monthly2026-07-18.xlsx
+++ b/PAMF_DIG F2 - monthly2026-07-18.xlsx
@@ -1290,7 +1290,7 @@
         <v>0.09</v>
       </c>
       <c r="N12" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>0.09</v>
       </c>
       <c r="N35" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         <v>0.09</v>
       </c>
       <c r="N38" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -3407,7 +3407,7 @@
         <v>0.09</v>
       </c>
       <c r="N41" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         <v>0.09</v>
       </c>
       <c r="N53" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -5159,7 +5159,7 @@
         <v>0.09</v>
       </c>
       <c r="N65" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
@@ -5743,7 +5743,7 @@
         <v>0.09</v>
       </c>
       <c r="N73" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
@@ -5816,7 +5816,7 @@
         <v>0.09</v>
       </c>
       <c r="N74" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         <v>0.09</v>
       </c>
       <c r="N81" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
@@ -7422,7 +7422,7 @@
         <v>0.09</v>
       </c>
       <c r="N96" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
@@ -7641,7 +7641,7 @@
         <v>0.09</v>
       </c>
       <c r="N99" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>0.09</v>
       </c>
       <c r="N108" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O108" t="inlineStr">
         <is>
@@ -9685,7 +9685,7 @@
         <v>0.09</v>
       </c>
       <c r="N127" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O127" t="inlineStr">
         <is>
@@ -11948,7 +11948,7 @@
         <v>0.09</v>
       </c>
       <c r="N158" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O158" t="inlineStr">
         <is>
@@ -12167,7 +12167,7 @@
         <v>0.09</v>
       </c>
       <c r="N161" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O161" t="inlineStr">
         <is>
@@ -13846,7 +13846,7 @@
         <v>0.09</v>
       </c>
       <c r="N184" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O184" t="inlineStr">
         <is>
@@ -15233,7 +15233,7 @@
         <v>0.09</v>
       </c>
       <c r="N203" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O203" t="inlineStr">
         <is>
@@ -15671,7 +15671,7 @@
         <v>0.09</v>
       </c>
       <c r="N209" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O209" t="inlineStr">
         <is>
@@ -17350,7 +17350,7 @@
         <v>0.09</v>
       </c>
       <c r="N232" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O232" t="inlineStr">
         <is>
@@ -17496,7 +17496,7 @@
         <v>0.09</v>
       </c>
       <c r="N234" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O234" t="inlineStr">
         <is>
@@ -18737,7 +18737,7 @@
         <v>0.09</v>
       </c>
       <c r="N251" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O251" t="inlineStr">
         <is>
@@ -20781,7 +20781,7 @@
         <v>0.09</v>
       </c>
       <c r="N279" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O279" t="inlineStr">
         <is>
@@ -21584,7 +21584,7 @@
         <v>0.09</v>
       </c>
       <c r="N290" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O290" t="inlineStr">
         <is>
@@ -23044,7 +23044,7 @@
         <v>0.09</v>
       </c>
       <c r="N310" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O310" t="inlineStr">
         <is>
